--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.63349819741252</v>
+        <v>9.365443457079534</v>
       </c>
       <c r="D2" t="n">
-        <v>56.72983087723441</v>
+        <v>9.218597517550592</v>
       </c>
       <c r="E2" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F2" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.83048780297919</v>
+        <v>9.072454267984117</v>
       </c>
       <c r="D3" t="n">
-        <v>55.0603097800433</v>
+        <v>8.947300339257037</v>
       </c>
       <c r="E3" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F3" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.48921941924491</v>
+        <v>6.416998155627298</v>
       </c>
       <c r="D4" t="n">
-        <v>39.10018828743421</v>
+        <v>6.353780596708059</v>
       </c>
       <c r="E4" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F4" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.32821539936257</v>
+        <v>3.628335002396417</v>
       </c>
       <c r="D5" t="n">
-        <v>21.67069600994187</v>
+        <v>3.521488101615554</v>
       </c>
       <c r="E5" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F5" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.83487915883295</v>
+        <v>3.223167863310354</v>
       </c>
       <c r="D6" t="n">
-        <v>18.93443737738658</v>
+        <v>3.076846073825319</v>
       </c>
       <c r="E6" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F6" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.44465334996907</v>
+        <v>5.922256169369975</v>
       </c>
       <c r="D7" t="n">
-        <v>36.22437564276336</v>
+        <v>5.886461041949047</v>
       </c>
       <c r="E7" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F7" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.75591715173871</v>
+        <v>2.397836537157541</v>
       </c>
       <c r="D8" t="n">
-        <v>14.56850042712243</v>
+        <v>2.367381319407395</v>
       </c>
       <c r="E8" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F8" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.75599057342537</v>
+        <v>2.235348468181623</v>
       </c>
       <c r="D9" t="n">
-        <v>14.28510113081112</v>
+        <v>2.321328933756808</v>
       </c>
       <c r="E9" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F9" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.03774181917892</v>
+        <v>2.931133045616574</v>
       </c>
       <c r="D10" t="n">
-        <v>18.23790509514792</v>
+        <v>2.963659577961536</v>
       </c>
       <c r="E10" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F10" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.5372650425934</v>
+        <v>5.612305569421428</v>
       </c>
       <c r="D11" t="n">
-        <v>34.98399629630048</v>
+        <v>5.684899398148827</v>
       </c>
       <c r="E11" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F11" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.72423198384571</v>
+        <v>2.555187697374928</v>
       </c>
       <c r="D12" t="n">
-        <v>16.52249392147517</v>
+        <v>2.684905262239716</v>
       </c>
       <c r="E12" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F12" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.66916706399518</v>
+        <v>4.821239647899216</v>
       </c>
       <c r="D13" t="n">
-        <v>30.44775891915946</v>
+        <v>4.947760824363412</v>
       </c>
       <c r="E13" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F13" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.81729666738371</v>
+        <v>6.470310708449853</v>
       </c>
       <c r="D14" t="n">
-        <v>40.49060660854966</v>
+        <v>6.57972357388932</v>
       </c>
       <c r="E14" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F14" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.23678664315968</v>
+        <v>6.863477829513449</v>
       </c>
       <c r="D15" t="n">
-        <v>43.10479625937302</v>
+        <v>7.004529392148116</v>
       </c>
       <c r="E15" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F15" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.75728929131346</v>
+        <v>9.385559509838439</v>
       </c>
       <c r="D16" t="n">
-        <v>58.64384575189035</v>
+        <v>9.529624934682182</v>
       </c>
       <c r="E16" t="n">
-        <v>15.17092714463903</v>
+        <v>2.465275661003843</v>
       </c>
       <c r="F16" t="n">
-        <v>15.11767912250533</v>
+        <v>2.456622857407117</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
